--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119530206</v>
+        <v>119529951</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1335,10 +1335,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548174</v>
+        <v>548438</v>
       </c>
       <c r="R7" t="n">
-        <v>6646078</v>
+        <v>6645891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1392,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ungefärligt antal</t>
+          <t>Ca 100 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,7 +1420,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119529951</v>
+        <v>119530206</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1451,14 +1455,10 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548438</v>
+        <v>548174</v>
       </c>
       <c r="R8" t="n">
-        <v>6645891</v>
+        <v>6646078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 100 plantor</t>
+          <t>Ungefärligt antal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119685500</v>
+        <v>119685461</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547821</v>
+        <v>547780</v>
       </c>
       <c r="R9" t="n">
-        <v>6646046</v>
+        <v>6646075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119685375</v>
+        <v>119686771</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,47 +1650,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Skummossen, Skummossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547775</v>
+        <v>548281</v>
       </c>
       <c r="R10" t="n">
-        <v>6646079</v>
+        <v>6645904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119685794</v>
+        <v>119685184</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1782,17 +1773,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Svedberget, Svedberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548123</v>
+        <v>547712</v>
       </c>
       <c r="R11" t="n">
-        <v>6646045</v>
+        <v>6646120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119685499</v>
+        <v>119685500</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547804</v>
+        <v>547821</v>
       </c>
       <c r="R12" t="n">
-        <v>6646030</v>
+        <v>6646046</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119685184</v>
+        <v>119685477</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1986,26 +1986,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svedberget, Svedberget, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547712</v>
+        <v>547805</v>
       </c>
       <c r="R13" t="n">
-        <v>6646120</v>
+        <v>6646059</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119685477</v>
+        <v>119685375</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2097,17 +2088,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547805</v>
+        <v>547775</v>
       </c>
       <c r="R14" t="n">
-        <v>6646059</v>
+        <v>6646079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119686771</v>
+        <v>119685794</v>
       </c>
       <c r="B15" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,38 +2178,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skummossen, Skummossen, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548281</v>
+        <v>548123</v>
       </c>
       <c r="R15" t="n">
-        <v>6645904</v>
+        <v>6646045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119685461</v>
+        <v>119685499</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547780</v>
+        <v>547804</v>
       </c>
       <c r="R17" t="n">
-        <v>6646075</v>
+        <v>6646030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -1536,7 +1536,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119685461</v>
+        <v>119685160</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1572,14 +1572,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Svedberget, Svedberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547780</v>
+        <v>547712</v>
       </c>
       <c r="R9" t="n">
-        <v>6646075</v>
+        <v>6646120</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119686771</v>
+        <v>119685499</v>
       </c>
       <c r="B10" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,38 +1650,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skummossen, Skummossen, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548281</v>
+        <v>547804</v>
       </c>
       <c r="R10" t="n">
-        <v>6645904</v>
+        <v>6646030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119685184</v>
+        <v>119685794</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1773,26 +1773,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svedberget, Svedberget, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547712</v>
+        <v>548123</v>
       </c>
       <c r="R11" t="n">
-        <v>6646120</v>
+        <v>6646045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1851,7 +1842,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119685500</v>
+        <v>119687621</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1884,17 +1875,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Skummossen, Skummossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547821</v>
+        <v>548544</v>
       </c>
       <c r="R12" t="n">
-        <v>6646046</v>
+        <v>6645782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119685375</v>
+        <v>119685461</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2088,26 +2088,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547775</v>
+        <v>547780</v>
       </c>
       <c r="R14" t="n">
-        <v>6646079</v>
+        <v>6646075</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2166,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119685794</v>
+        <v>119686771</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,38 +2169,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Skummossen, Skummossen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548123</v>
+        <v>548281</v>
       </c>
       <c r="R15" t="n">
-        <v>6646045</v>
+        <v>6645904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119687621</v>
+        <v>119685375</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2303,7 +2294,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2313,14 +2304,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skummossen, Skummossen, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548544</v>
+        <v>547775</v>
       </c>
       <c r="R16" t="n">
-        <v>6645782</v>
+        <v>6646079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2370,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119685499</v>
+        <v>119685500</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2419,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547804</v>
+        <v>547821</v>
       </c>
       <c r="R17" t="n">
-        <v>6646030</v>
+        <v>6646046</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -1536,10 +1536,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119685160</v>
+        <v>119686771</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,38 +1548,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svedberget, Svedberget, Vstm</t>
+          <t>Skummossen, Skummossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547712</v>
+        <v>548281</v>
       </c>
       <c r="R9" t="n">
-        <v>6646120</v>
+        <v>6645904</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119685499</v>
+        <v>119685461</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547804</v>
+        <v>547780</v>
       </c>
       <c r="R10" t="n">
-        <v>6646030</v>
+        <v>6646075</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119685794</v>
+        <v>119685499</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548123</v>
+        <v>547804</v>
       </c>
       <c r="R11" t="n">
-        <v>6646045</v>
+        <v>6646030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119685477</v>
+        <v>119685184</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1986,17 +1986,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bovallen, Bovallen, Vstm</t>
+          <t>Svedberget, Svedberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547805</v>
+        <v>547712</v>
       </c>
       <c r="R13" t="n">
-        <v>6646059</v>
+        <v>6646120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,7 +2064,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119685461</v>
+        <v>119685477</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2095,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547780</v>
+        <v>547805</v>
       </c>
       <c r="R14" t="n">
-        <v>6646075</v>
+        <v>6646059</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119686771</v>
+        <v>119685794</v>
       </c>
       <c r="B15" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2178,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skummossen, Skummossen, Vstm</t>
+          <t>Bovallen, Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548281</v>
+        <v>548123</v>
       </c>
       <c r="R15" t="n">
-        <v>6645904</v>
+        <v>6646045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>121155617</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>121200560</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>121194443</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2699,7 +2699,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121200560</v>
+        <v>121194443</v>
       </c>
       <c r="B20" t="n">
         <v>98081</v>
@@ -2732,21 +2732,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bovallen 5 (knärot), Vstm</t>
+          <t>Svedberget (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548121</v>
+        <v>547712</v>
       </c>
       <c r="R20" t="n">
-        <v>6646045</v>
+        <v>6646121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2781,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>U-Fag-0335</t>
+          <t>U-Fag-0332</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2815,7 +2823,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121194443</v>
+        <v>121200560</v>
       </c>
       <c r="B21" t="n">
         <v>98081</v>
@@ -2848,29 +2856,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svedberget (knärot), Vstm</t>
+          <t>Bovallen 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547712</v>
+        <v>548121</v>
       </c>
       <c r="R21" t="n">
-        <v>6646121</v>
+        <v>6646045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>U-Fag-0332</t>
+          <t>U-Fag-0335</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>121155617</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>121194443</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>121200560</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>121155617</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121194443</v>
+        <v>121200560</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,29 +2732,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svedberget (knärot), Vstm</t>
+          <t>Bovallen 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547712</v>
+        <v>548121</v>
       </c>
       <c r="R20" t="n">
-        <v>6646121</v>
+        <v>6646045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2773,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>U-Fag-0332</t>
+          <t>U-Fag-0335</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2823,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121200560</v>
+        <v>121194443</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,21 +2848,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bovallen 5 (knärot), Vstm</t>
+          <t>Svedberget (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548121</v>
+        <v>547712</v>
       </c>
       <c r="R21" t="n">
-        <v>6646045</v>
+        <v>6646121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>U-Fag-0335</t>
+          <t>U-Fag-0332</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
         <v>121155617</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121200560</v>
+        <v>121194443</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bovallen 5 (knärot), Vstm</t>
+          <t>Svedberget (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>548121</v>
+        <v>547712</v>
       </c>
       <c r="R20" t="n">
-        <v>6646045</v>
+        <v>6646121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2781,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>U-Fag-0335</t>
+          <t>U-Fag-0332</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2815,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121194443</v>
+        <v>121200560</v>
       </c>
       <c r="B21" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,29 +2856,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svedberget (knärot), Vstm</t>
+          <t>Bovallen 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547712</v>
+        <v>548121</v>
       </c>
       <c r="R21" t="n">
-        <v>6646121</v>
+        <v>6646045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>U-Fag-0332</t>
+          <t>U-Fag-0335</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121194443</v>
+        <v>121200560</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,29 +2732,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svedberget (knärot), Vstm</t>
+          <t>Bovallen 5 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547712</v>
+        <v>548121</v>
       </c>
       <c r="R20" t="n">
-        <v>6646121</v>
+        <v>6646045</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2773,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>U-Fag-0332</t>
+          <t>U-Fag-0335</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2823,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121200560</v>
+        <v>121194443</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,21 +2848,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bovallen 5 (knärot), Vstm</t>
+          <t>Svedberget (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548121</v>
+        <v>547712</v>
       </c>
       <c r="R21" t="n">
-        <v>6646045</v>
+        <v>6646121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>U-Fag-0335</t>
+          <t>U-Fag-0332</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24847-2024 artfynd.xlsx
+++ b/artfynd/A 24847-2024 artfynd.xlsx
@@ -2702,7 +2702,7 @@
         <v>121200560</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>121194443</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>121209425</v>
       </c>
       <c r="B22" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
